--- a/jogos_2025-06-07.xlsx
+++ b/jogos_2025-06-07.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Imabari</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="M5" t="n">
-        <v>3.64</v>
+        <v>2.93</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="O5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y5" t="n">
         <v>2.6</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="Z5" t="n">
-        <v>2.32</v>
+        <v>1.43</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>4.85</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['46', '64']</t>
-        </is>
-      </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.01</v>
+        <v>2.54</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45815.25</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Imabari</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="M6" t="n">
-        <v>2.93</v>
+        <v>3.64</v>
       </c>
       <c r="N6" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.45</v>
+        <v>3.35</v>
       </c>
       <c r="R6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB6" t="n">
         <v>1.55</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="AC6" t="n">
         <v>1.5</v>
       </c>
-      <c r="X6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.12</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '64']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.54</v>
+        <v>2.01</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45815.25</v>
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,22 +1959,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.6</v>
+        <v>1.07</v>
       </c>
       <c r="M12" t="n">
-        <v>3.73</v>
+        <v>9.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="O12" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="P12" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.8</v>
+        <v>3.09</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2017,12 +2017,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['42', '65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['66']</t>
         </is>
       </c>
       <c r="AG12" t="n">
@@ -2032,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45815.375</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.07</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>9.5</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>2.54</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>3.39</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.09</v>
+        <v>2.11</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>2.67</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.43</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '70']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['66']</t>
+          <t>['16', '84', '90+1']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.13</v>
+        <v>1.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45815.375</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,19 +2191,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.54</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.39</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['28', '70']</t>
+          <t>['42', '65']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['16', '84', '90+1']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45815.375</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,16 +3352,16 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.05</v>
+        <v>3.38</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="O23" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
         <v>3.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="U23" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X23" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.85</v>
+        <v>2.59</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD23" t="n">
         <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.4</v>
+        <v>1.73</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45815.79166666666</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,16 +3481,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.38</v>
+        <v>3.05</v>
       </c>
       <c r="M24" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="O24" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
         <v>3.2</v>
       </c>
       <c r="T24" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="U24" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
         <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AD24" t="n">
         <v>2.2</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['44']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45815.79166666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M26" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="N26" t="n">
-        <v>7.19</v>
+        <v>8.18</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>7</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q26" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U26" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="X26" t="n">
-        <v>3.07</v>
+        <v>3.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
+          <t>['90+9']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['54']</t>
         </is>
       </c>
       <c r="AG26" t="n">
         <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.92</v>
+        <v>4.33</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45815.83333333334</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.34</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>4.45</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
-        <v>8.18</v>
+        <v>3.65</v>
       </c>
       <c r="O27" t="n">
-        <v>1.62</v>
+        <v>2.84</v>
       </c>
       <c r="P27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X27" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q27" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T27" t="n">
+      <c r="Y27" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['37', '66']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['90+9']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45815.83333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,34 +4023,34 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="N28" t="n">
-        <v>6.47</v>
+        <v>7.19</v>
       </c>
       <c r="O28" t="n">
         <v>1.8</v>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.25</v>
+        <v>5.7</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S28" t="n">
-        <v>3.6</v>
+        <v>3.13</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="U28" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="V28" t="n">
         <v>1.01</v>
@@ -4059,47 +4059,47 @@
         <v>1.14</v>
       </c>
       <c r="X28" t="n">
-        <v>4.8</v>
+        <v>3.07</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['28', '54', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['7', '20', '33']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45815.83333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="N29" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T29" t="n">
         <v>2.1</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>2.4</v>
+        <v>4.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.56</v>
+        <v>1.49</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.48</v>
+        <v>2.35</v>
       </c>
       <c r="AA29" t="n">
-        <v>4.75</v>
+        <v>2.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.17</v>
+        <v>1.66</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['37', '66']</t>
+          <t>['28', '54', '80']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '20', '33']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.73</v>
+        <v>2.61</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45815.83333333334</v>
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.99</v>
+        <v>2.43</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N32" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.3</v>
       </c>
-      <c r="O32" t="n">
-        <v>3</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.43</v>
-      </c>
       <c r="Q32" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T32" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X32" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4602,20 +4602,20 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['8', '23', '30', '44', '56', '65', '90+1']</t>
+          <t>['8', '23', '30', '44', '56', '65', '9001']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45815.85416666666</v>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Las Vegas Lights</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="M35" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>2.87</v>
+        <v>4.15</v>
       </c>
       <c r="O35" t="n">
-        <v>2.73</v>
+        <v>2.45</v>
       </c>
       <c r="P35" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.66</v>
+        <v>5.33</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T35" t="n">
-        <v>2.7</v>
+        <v>2.98</v>
       </c>
       <c r="U35" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W35" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X35" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.82</v>
+        <v>2.06</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AA35" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['13', '27', '61']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45815.91666666666</v>
@@ -5029,109 +5029,109 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O36" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA36" t="n">
         <v>3</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="M36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.58</v>
-      </c>
       <c r="AB36" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AC36" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['13', '27', '61']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH36" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AI36" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ36" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45815.91666666666</v>
@@ -5170,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="M37" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="N37" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="O37" t="n">
         <v>2.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
         <v>2.75</v>
       </c>
       <c r="U37" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W37" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X37" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AC37" t="n">
         <v>1.75</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5247,20 +5247,20 @@
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['6', '66']</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45815.9375</v>
